--- a/excel/files_08_data_analysis/examples.xlsx
+++ b/excel/files_08_data_analysis/examples.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hanzenl-my.sharepoint.com/personal/j_hageman_pl_hanze_nl/Documents/web_pages/data_analysis_bml-r/data_analysis_bml/excel/files_08_data_analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63" documentId="8_{3B6CB5D2-D69F-49A5-A383-7E44225A4FE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39C2A4C3-7A45-430F-94C8-B5A75CDDA92F}"/>
+  <xr:revisionPtr revIDLastSave="68" documentId="8_{3B6CB5D2-D69F-49A5-A383-7E44225A4FE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C60FB0D-EE01-4A50-B534-F527A48D28F6}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{EECC7863-79BC-4C52-BFCC-4F50C68B49DC}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="16">
   <si>
     <t>Number of zebrafish</t>
   </si>
@@ -484,7 +484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F16F95C-C5F5-4083-BF39-9825B5A7F360}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
@@ -524,6 +524,10 @@
       <c r="D2">
         <v>0.13400000000000001</v>
       </c>
+      <c r="E2">
+        <f>C2*D2</f>
+        <v>1.6080000000000001</v>
+      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3">
@@ -538,6 +542,10 @@
       <c r="D3">
         <v>7.9000000000000001E-2</v>
       </c>
+      <c r="E3">
+        <f t="shared" ref="E3:E5" si="0">C3*D3</f>
+        <v>1.1060000000000001</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4">
@@ -552,6 +560,10 @@
       <c r="D4">
         <v>0.154</v>
       </c>
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>5.0819999999999999</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5">
@@ -566,13 +578,26 @@
       <c r="D5">
         <v>0.16200000000000001</v>
       </c>
+      <c r="E5">
+        <f t="shared" si="0"/>
+        <v>3.8879999999999999</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="D6" t="s">
         <v>8</v>
       </c>
-      <c r="E6" cm="1">
-        <f t="array" ref="E6">SUM(C2:C5*D2:D5)</f>
+      <c r="E6">
+        <f>SUM(E2:E5)</f>
+        <v>11.684000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="D9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" cm="1">
+        <f t="array" ref="E9">SUM(C2:C5*D2:D5)</f>
         <v>11.684000000000001</v>
       </c>
     </row>

--- a/excel/files_08_data_analysis/examples.xlsx
+++ b/excel/files_08_data_analysis/examples.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hanzenl-my.sharepoint.com/personal/j_hageman_pl_hanze_nl/Documents/web_pages/data_analysis_bml-r/data_analysis_bml/excel/files_08_data_analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="68" documentId="8_{3B6CB5D2-D69F-49A5-A383-7E44225A4FE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C60FB0D-EE01-4A50-B534-F527A48D28F6}"/>
+  <xr:revisionPtr revIDLastSave="79" documentId="8_{3B6CB5D2-D69F-49A5-A383-7E44225A4FE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1E4EB9F-5E4E-467F-836A-1EC21DA22EA6}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{EECC7863-79BC-4C52-BFCC-4F50C68B49DC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="6" xr2:uid="{EECC7863-79BC-4C52-BFCC-4F50C68B49DC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,8 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
     <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
     <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet6" sheetId="6" r:id="rId6"/>
+    <sheet name="Sheet7" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -695,9 +697,9 @@
       <c r="D6" t="s">
         <v>8</v>
       </c>
-      <c r="E6">
-        <f t="array" ref="E6">SUM(C2:C5,D2:D5)</f>
-        <v>83.528999999999996</v>
+      <c r="E6" cm="1">
+        <f t="array" ref="E6">SUM(C2:C5*D2:D5)</f>
+        <v>11.684000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -955,4 +957,156 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0E11E5D-1D30-4EAC-82FD-CD224ECFB60B}">
+  <dimension ref="A1:A10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" cm="1">
+        <f t="array" ref="A1:A10">ROW(1:10)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8344E4FA-27F5-4BDE-9736-FF7AD481BA1C}">
+  <dimension ref="A1:L10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A1">
+        <v>1</v>
+      </c>
+      <c r="C1" cm="1">
+        <f t="array" ref="C1:L1">TRANSPOSE(A1:A10)</f>
+        <v>1</v>
+      </c>
+      <c r="D1">
+        <v>2</v>
+      </c>
+      <c r="E1">
+        <v>3</v>
+      </c>
+      <c r="F1">
+        <v>4</v>
+      </c>
+      <c r="G1">
+        <v>5</v>
+      </c>
+      <c r="H1">
+        <v>6</v>
+      </c>
+      <c r="I1">
+        <v>7</v>
+      </c>
+      <c r="J1">
+        <v>8</v>
+      </c>
+      <c r="K1">
+        <v>9</v>
+      </c>
+      <c r="L1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>